--- a/docs/Unit_Test_Plan.xlsx
+++ b/docs/Unit_Test_Plan.xlsx
@@ -449,15 +449,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,27 +498,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>UT-RAG-001: PDF Chunking and Overlap</t>
+          <t>UT-RAG-001: PDF Chunking size and overlap</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Upload a sample PDF document containing 2000 characters. Inspect generated chunks in MongoDB.</t>
+          <t>Upload a sample PDF document containing 2000 characters. Inspect generated chunks in MongoDB database.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Each chunk size &lt;= 500 characters and overlapping character length = 100.</t>
+          <t>Each segment text length &lt;= 500 characters and overlap overlap character count == 100.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>4 text chunks generated, each chunk overlapping with its predecessor by 100 characters.</t>
+          <t>4 text chunks generated, each chunk overlapping with its predecessor by exactly 100 characters.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Passed. Chunks generated with correct size and overlap.</t>
+          <t>Passed. Verified chunk sizes and overlap offsets using document validator.</t>
         </is>
       </c>
     </row>
@@ -528,27 +528,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>UT-RAG-002: Vector Embeddings Generation</t>
+          <t>UT-SIM-001: Customer Simulator Mood Adjustment</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Call embedding generator function with test string. Check output dimensions.</t>
+          <t>Post message to simulator session with highly empathetic agent message. Inspect returned customer frustration score.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Model all-MiniLM-L6-v2 produces exactly 384-dimensional vector coordinate array.</t>
+          <t>Frustration score decreases (e.g. from 7.0 to 5.0) on receipt of empathetic statement.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Vector array of float values with length == 384 returned.</t>
+          <t>Simulator updates frustration levels and adjusts its tone to be cooperative.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Passed. Vector array dimensions are exactly 384.</t>
+          <t>Passed. Customer emotional progression responds dynamically to agent tone.</t>
         </is>
       </c>
     </row>
@@ -558,27 +558,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>UT-AUTH-001: User Password Hashing</t>
+          <t>UT-GRAPH-001: LangGraph Parallel Node Execution state merge</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Call /api/auth/register with standard user payload. Query database for hashed password.</t>
+          <t>Trigger concurrent execution of parallel intent, sentiment, and escalation risk nodes. Check combined output state.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Hashed password starts with $2b$ indicating bcrypt hashing.</t>
+          <t>State dictionary reducer joins parallel outputs without data overwrites.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hashed password stored in database; plain text password is not visible.</t>
+          <t>Graph state maps all combined analysis results (intent category, sentiment score, escalation risk score) in a single dict.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Passed. Bcrypt hashing verified.</t>
+          <t>Passed. Parallel execution state merges cleanly.</t>
         </is>
       </c>
     </row>
@@ -588,147 +588,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>UT-RAG-003: Similarity Score Threshold Filter</t>
+          <t>UT-ANALYTICS-001: Post-Call Session Summary Generation</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Query vector database with search term. Match result scores.</t>
+          <t>Close active session by posting status change. Verify summary agent response.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Filter out and do not display recommendations with similarity score below 0.40.</t>
+          <t>MongoDB database saves complete session report with aggregate compliance, frustration deltas, and duration.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Returns only documents with cosine similarity &gt;= 0.40; low similarity matches logged as gap.</t>
+          <t>Creates a completed QA report record linked to user sessions collection.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Passed. Scores below 0.40 correctly filtered out.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>UT-SIM-001: Customer Simulator Mood Evolution</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Inject an empathetic agent response ('I understand and apologize for this double charge') into active session. Check updated frustration score.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Frustration score decreases after receiving empathetic response.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Customer frustration score drops from 7.0 to 5.0.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Passed. Mood adjusted correctly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>UT-SIM-002: Customer Simulator Persona Consistency</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Input a policy violation ('I can refund you the double charge in 5 seconds'). Trigger customer simulator response.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Simulator stays in persona and does not accept fake refund timelines.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Simulator rejects the unrealistic timeline, staying consistent with persona guidelines.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Passed. Simulator output matches persona expectations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>UT-GRAPH-001: LangGraph Parallel Execution state merge</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Trigger parallel nodes (Intent + Sentiment + Risk) simultaneously. Verify combined state.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Merges output dictionaries into active state without overwriting prior outputs.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>State dict contains all values from Intent, Sentiment, and Risk.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Passed. Graph merged outputs successfully.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>UT-AUTH-002: JWT Token Expiration and Verification</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Submit expired JWT token to /api/users/me endpoint.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Submit expired JWT token.</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Returns HTTP 401 response with 'Token has expired' message.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Passed. Unauthorized access blocked.</t>
+          <t>Passed. Database updates summary and maps QA telemetry successfully.</t>
         </is>
       </c>
     </row>
